--- a/reconcile/storage/output/ongoing/ongoing_battery_by_inst_q.xlsx
+++ b/reconcile/storage/output/ongoing/ongoing_battery_by_inst_q.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL21"/>
+  <dimension ref="A1:BM21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,200 +557,205 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>ford</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>forsee power</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>fpt industrial</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>fraunhofer ffb</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>freyr</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>gotion high tech</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>gotion inobat batteries</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>green cell</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hyundai mobis</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>impact clean power technology</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>inobat</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>international power supply</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>lg energy solution</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>lion smart</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>lux optimeyes energy</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>lyten</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>man</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>microvast</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>morrow batteries</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>norcsi</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>northvolt</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>porsche</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>prime batteries technology</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>projinko</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>rwe</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>samsung sdi</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>seat</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>sia “ecolead”</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>siemens</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sk innovation</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>skoda</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stellantis</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sunlight group</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>tiamat</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>uk battery industrialisation centre</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>valmet automotive</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>verkor</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>vianode</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>volklec</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>volkswagen</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>volvo</t>
         </is>
@@ -782,7 +787,7 @@
         <v>64583333.33333333</v>
       </c>
       <c r="I2" t="n">
-        <v>337868.2764212993</v>
+        <v>337868.25</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -830,14 +835,14 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1666666.666666667</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>5000000</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
@@ -848,17 +853,17 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
         <v>312500</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
@@ -878,20 +883,20 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
         <v>7142857.142857143</v>
       </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>314254807.6923077</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
@@ -899,13 +904,13 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
         <v>750000</v>
       </c>
-      <c r="AW2" t="n">
-        <v>54957900.39412397</v>
-      </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>54957900.375</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -914,14 +919,14 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>45792604.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
+        <v>45792604.56521739</v>
+      </c>
+      <c r="BC2" t="n">
         <v>16250000</v>
       </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -929,14 +934,14 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>147392290.2494331</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
+        <v>147392290</v>
+      </c>
+      <c r="BH2" t="n">
         <v>15000000</v>
       </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
@@ -944,9 +949,12 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
         <v>52941176.47058824</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1024,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>5000000</v>
+        <v>15580692.41666667</v>
       </c>
       <c r="Z3" t="n">
         <v>5000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -1042,32 +1050,32 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
         <v>312500</v>
       </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>474756179.1555439</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
         <v>416666.6666666667</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
@@ -1081,23 +1089,23 @@
         <v>0</v>
       </c>
       <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>309879807.6923077</v>
       </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>416666.6666666667</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>750000</v>
       </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
@@ -1108,14 +1116,14 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>45792604.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
+        <v>45792604.56521739</v>
+      </c>
+      <c r="BC3" t="n">
         <v>16250000</v>
       </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
@@ -1126,11 +1134,11 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
         <v>15000000</v>
       </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
@@ -1141,6 +1149,9 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1218,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>5000000</v>
+        <v>46742077.25</v>
       </c>
       <c r="Z4" t="n">
         <v>5000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1236,32 +1247,32 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>312500</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>474756179.1555439</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>625000</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
@@ -1275,56 +1286,56 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>307692307.6923077</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>625000</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>750000</v>
       </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>181666.6666666667</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
       <c r="BA4" t="n">
-        <v>45792604.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
+        <v>45792604.56521739</v>
+      </c>
+      <c r="BC4" t="n">
         <v>16250000</v>
       </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
       <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
         <v>2083333.333333333</v>
       </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
         <v>10000000</v>
       </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
@@ -1335,6 +1346,9 @@
         <v>0</v>
       </c>
       <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1346,7 +1360,7 @@
         <v>625000</v>
       </c>
       <c r="C5" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1412,13 +1426,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>5000000</v>
+        <v>46742077.25</v>
       </c>
       <c r="Z5" t="n">
         <v>5000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1430,32 +1444,32 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
         <v>312500</v>
       </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>474756179.1555439</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>625000</v>
       </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
@@ -1469,47 +1483,47 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>381948773.2095491</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>381948773.1923077</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>625000</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>750000</v>
       </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>545000</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
       <c r="BA5" t="n">
-        <v>45792604.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
+        <v>45792604.56521739</v>
+      </c>
+      <c r="BC5" t="n">
         <v>16250000</v>
       </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
       <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
         <v>6250000</v>
       </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1529,6 +1543,9 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1540,7 +1557,7 @@
         <v>625000</v>
       </c>
       <c r="C6" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1606,13 +1623,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>5000000</v>
+        <v>46742077.25</v>
       </c>
       <c r="Z6" t="n">
         <v>5000000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1624,32 +1641,32 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>312500</v>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>474756179.1555439</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>625000</v>
       </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
@@ -1663,20 +1680,20 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>74256465.51724139</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>74256465.5</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
       <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>625000</v>
       </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
@@ -1684,26 +1701,26 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>545000</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
       <c r="BA6" t="n">
-        <v>96511354.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
+        <v>96511354.56521739</v>
+      </c>
+      <c r="BC6" t="n">
         <v>16250000</v>
       </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
       <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
         <v>6250000</v>
       </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1723,6 +1740,9 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1734,7 +1754,7 @@
         <v>625000</v>
       </c>
       <c r="C7" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1800,23 +1820,23 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>5000000</v>
+        <v>46742077.25</v>
       </c>
       <c r="Z7" t="n">
         <v>5000000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
         <v>13333333.33333333</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
@@ -1824,26 +1844,26 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>474756179.1555439</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>474756179.1176471</v>
       </c>
       <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>625000</v>
       </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
@@ -1857,20 +1877,20 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>74256465.51724139</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>74256465.5</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>625000</v>
       </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
@@ -1878,26 +1898,26 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>545000</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
       <c r="BA7" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5416666.666666667</v>
       </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
       <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
         <v>6250000</v>
       </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1917,6 +1937,9 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1928,7 +1951,7 @@
         <v>625000</v>
       </c>
       <c r="C8" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1994,23 +2017,23 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>5000000</v>
+        <v>46742077.25</v>
       </c>
       <c r="Z8" t="n">
         <v>5000000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
         <v>40000000</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
@@ -2018,26 +2041,26 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>316504119.4370292</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>316504119.4117647</v>
       </c>
       <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
         <v>625000</v>
       </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
@@ -2051,20 +2074,20 @@
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>74256465.51724139</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
+        <v>74256465.5</v>
+      </c>
+      <c r="AT8" t="n">
         <v>16666.66666666667</v>
       </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
       <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>625000</v>
       </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
@@ -2072,26 +2095,26 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>545000</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
       <c r="BA8" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
         <v>14583333.33333333</v>
       </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -2108,9 +2131,12 @@
         <v>0</v>
       </c>
       <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
         <v>250000000</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BM8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2122,7 +2148,7 @@
         <v>625000</v>
       </c>
       <c r="C9" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2143,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>125147058.8235294</v>
+        <v>31029411.76470588</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2188,11 +2214,11 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="Z9" t="n">
         <v>5000000</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
@@ -2200,11 +2226,11 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
+        <v>147988649.2380952</v>
+      </c>
+      <c r="AD9" t="n">
         <v>40000000</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
@@ -2212,26 +2238,26 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>10000000</v>
       </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
         <v>12121212.12121212</v>
       </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
       <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
         <v>625000</v>
       </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
@@ -2239,26 +2265,26 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>40666666.66666666</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
       <c r="AR9" t="n">
-        <v>74256465.51724139</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
+        <v>74256465.5</v>
+      </c>
+      <c r="AT9" t="n">
         <v>25000</v>
       </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
       <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>625000</v>
       </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
@@ -2266,26 +2292,26 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>545000</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
       <c r="BA9" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC9" t="n">
         <v>6445833.333333333</v>
       </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
       <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
         <v>18750000</v>
       </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
@@ -2293,18 +2319,21 @@
         <v>0</v>
       </c>
       <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
         <v>12500000</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BJ9" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>0</v>
-      </c>
       <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
         <v>250000000</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BM9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2316,7 +2345,7 @@
         <v>625000</v>
       </c>
       <c r="C10" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2337,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>183970588.2352941</v>
+        <v>42794117.64705882</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2382,11 +2411,11 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
+        <v>46742077.25</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3333333.333333333</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
@@ -2394,11 +2423,11 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AD10" t="n">
         <v>40000000</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
@@ -2415,17 +2444,17 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
       <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
         <v>625000</v>
       </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
@@ -2433,26 +2462,26 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>61000000</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
       <c r="AR10" t="n">
-        <v>74256465.51724139</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
+        <v>74256465.5</v>
+      </c>
+      <c r="AT10" t="n">
         <v>25000</v>
       </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
       <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>625000</v>
       </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
       <c r="AW10" t="n">
         <v>0</v>
       </c>
@@ -2460,26 +2489,26 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>545000</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
       <c r="BA10" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC10" t="n">
         <v>19337500</v>
       </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
       <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
         <v>18750000</v>
       </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
@@ -2487,18 +2516,21 @@
         <v>0</v>
       </c>
       <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
         <v>18750000</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BJ10" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>0</v>
-      </c>
       <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
         <v>395833333.3333334</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BM10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2510,7 +2542,7 @@
         <v>208333.3333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2531,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>183970588.2352941</v>
+        <v>42794117.64705882</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -2576,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>31161384.83333333</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2588,11 +2620,11 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AD11" t="n">
         <v>40000000</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
@@ -2609,71 +2641,71 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
       <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
         <v>208333.3333333333</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>10000000</v>
       </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>61000000</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
       <c r="AR11" t="n">
-        <v>74256465.51724139</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
+        <v>74256465.5</v>
+      </c>
+      <c r="AT11" t="n">
         <v>25000</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>19166666.66666667</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>208333.3333333333</v>
       </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
       <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
         <v>28750000</v>
       </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
       <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>545000</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
       <c r="BA11" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC11" t="n">
         <v>19337500</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
         <v>18750000</v>
       </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
@@ -2681,18 +2713,21 @@
         <v>0</v>
       </c>
       <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
         <v>58750000</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BJ11" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>0</v>
-      </c>
       <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
         <v>687500000</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BM11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2704,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -2725,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>183970588.2352941</v>
+        <v>42794117.64705882</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -2782,11 +2817,11 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
+        <v>221982973.8571428</v>
+      </c>
+      <c r="AD12" t="n">
         <v>26666666.66666667</v>
       </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
@@ -2803,71 +2838,71 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
         <v>30000000</v>
       </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>61000000</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
       <c r="AR12" t="n">
-        <v>74256465.51724139</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
+        <v>74256465.5</v>
+      </c>
+      <c r="AT12" t="n">
         <v>25000</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>28750000</v>
       </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
         <v>43125000</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>363333.3333333333</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
       <c r="BA12" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC12" t="n">
         <v>19337500</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BD12" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BE12" t="n">
         <v>16666666.66666667</v>
       </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
@@ -2875,18 +2910,21 @@
         <v>0</v>
       </c>
       <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
         <v>138750000</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BJ12" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
       <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
         <v>687500000</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BM12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2919,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>183970588.2352941</v>
+        <v>42794117.64705882</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2943,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2976,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2997,71 +3035,71 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
         <v>30000000</v>
       </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>61000000</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
       <c r="AR13" t="n">
         <v>0</v>
       </c>
       <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
         <v>25000</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>28750000</v>
       </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
       <c r="AV13" t="n">
         <v>0</v>
       </c>
       <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
         <v>43125000</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC13" t="n">
         <v>19337500</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
         <v>12500000</v>
       </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
@@ -3069,18 +3107,21 @@
         <v>0</v>
       </c>
       <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
         <v>138750000</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BJ13" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
       <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
         <v>687500000</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BM13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3095,7 +3136,7 @@
         <v>205263157.8947369</v>
       </c>
       <c r="D14" t="n">
-        <v>388138487.8124514</v>
+        <v>388138487.8333333</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3113,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>183970588.2352941</v>
+        <v>42794117.64705882</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -3137,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3170,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3191,71 +3232,71 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
         <v>30000000</v>
       </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>61000000</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
       <c r="AR14" t="n">
         <v>0</v>
       </c>
       <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
         <v>25000</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>28750000</v>
       </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
         <v>43125000</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC14" t="n">
         <v>19337500</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BD14" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BE14" t="n">
         <v>12500000</v>
       </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
       <c r="BF14" t="n">
         <v>0</v>
       </c>
@@ -3263,18 +3304,21 @@
         <v>0</v>
       </c>
       <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
         <v>138750000</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BJ14" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ14" t="n">
-        <v>0</v>
-      </c>
       <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
         <v>687500000</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BM14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3289,7 +3333,7 @@
         <v>205263157.8947369</v>
       </c>
       <c r="D15" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3307,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>178970588.2352941</v>
+        <v>37794117.64705882</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -3331,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3364,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>221982973.8571428</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3373,11 +3417,11 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
         <v>15000000</v>
       </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
@@ -3385,71 +3429,71 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
         <v>30000000</v>
       </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>61000000</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
       <c r="AR15" t="n">
         <v>0</v>
       </c>
       <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
         <v>25000</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>28750000</v>
       </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
       <c r="AV15" t="n">
         <v>0</v>
       </c>
       <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
         <v>43125000</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC15" t="n">
         <v>19337500</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BD15" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
         <v>12500000</v>
       </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
@@ -3457,18 +3501,21 @@
         <v>0</v>
       </c>
       <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
         <v>138750000</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BJ15" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>0</v>
-      </c>
       <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
         <v>687500000</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BM15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3480,16 +3527,16 @@
         <v>125000000</v>
       </c>
       <c r="C16" t="n">
-        <v>333229653.9394088</v>
+        <v>333229653.8947368</v>
       </c>
       <c r="D16" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>28966961.37738483</v>
+        <v>28966961.375</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -3501,10 +3548,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>176470588.2352941</v>
+        <v>35294117.64705882</v>
       </c>
       <c r="K16" t="n">
-        <v>1877348.40029762</v>
+        <v>1877348.375</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3525,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3558,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>73994324.61904761</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -3567,11 +3614,11 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
         <v>15000000</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
@@ -3579,71 +3626,71 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
         <v>30000000</v>
       </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>20333333.33333333</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
       <c r="AR16" t="n">
         <v>0</v>
       </c>
       <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
         <v>8333.333333333334</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>28750000</v>
       </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
       <c r="AV16" t="n">
         <v>0</v>
       </c>
       <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
         <v>43125000</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AY16" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>197948854.5670491</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
+        <v>197948854.5652174</v>
+      </c>
+      <c r="BC16" t="n">
         <v>19337500</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BE16" t="n">
         <v>4166666.666666667</v>
       </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
       <c r="BF16" t="n">
         <v>0</v>
       </c>
@@ -3651,18 +3698,21 @@
         <v>0</v>
       </c>
       <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
         <v>138750000</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BJ16" t="n">
         <v>24375000</v>
       </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
       <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
         <v>437500000</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BM16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3674,16 +3724,16 @@
         <v>125000000</v>
       </c>
       <c r="C17" t="n">
-        <v>333229653.9394088</v>
+        <v>333229653.8947368</v>
       </c>
       <c r="D17" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>28966961.37738483</v>
+        <v>28966961.375</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -3695,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>184803921.5686274</v>
+        <v>43627450.98039216</v>
       </c>
       <c r="K17" t="n">
-        <v>1877348.40029762</v>
+        <v>1877348.375</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3719,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3755,17 +3805,17 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
         <v>51250000</v>
       </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
       <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
         <v>15000000</v>
       </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
@@ -3773,23 +3823,23 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
         <v>30000000</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AO17" t="n">
         <v>40000000</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
@@ -3803,38 +3853,38 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
         <v>28750000</v>
       </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
       <c r="AV17" t="n">
         <v>0</v>
       </c>
       <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
         <v>43125000</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AY17" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>65982951.5223497</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
+        <v>65982951.52173913</v>
+      </c>
+      <c r="BC17" t="n">
         <v>12891666.66666667</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
@@ -3845,18 +3895,21 @@
         <v>0</v>
       </c>
       <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
         <v>126250000</v>
       </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ17" t="n">
         <v>0</v>
       </c>
       <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
         <v>437500000</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BM17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3868,16 +3921,16 @@
         <v>125000000</v>
       </c>
       <c r="C18" t="n">
-        <v>333229653.9394088</v>
+        <v>333229653.8947368</v>
       </c>
       <c r="D18" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>28966961.37738483</v>
+        <v>28966961.375</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3889,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>188970588.2352941</v>
+        <v>47794117.64705882</v>
       </c>
       <c r="K18" t="n">
-        <v>1877348.40029762</v>
+        <v>1877348.375</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3913,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3949,17 +4002,17 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
         <v>153750000</v>
       </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
       <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
         <v>15000000</v>
       </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
       <c r="AH18" t="n">
         <v>0</v>
       </c>
@@ -3967,23 +4020,23 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
         <v>30000000</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>60000000</v>
       </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
@@ -3997,23 +4050,23 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
         <v>28750000</v>
       </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
       <c r="AV18" t="n">
         <v>0</v>
       </c>
       <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
         <v>43125000</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AY18" t="n">
         <v>40909090.90909091</v>
       </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
@@ -4024,11 +4077,11 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
         <v>14875000</v>
       </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
@@ -4039,19 +4092,22 @@
         <v>0</v>
       </c>
       <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
         <v>120000000</v>
       </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ18" t="n">
         <v>0</v>
       </c>
       <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
         <v>291666666.6666667</v>
       </c>
-      <c r="BL18" t="n">
-        <v>362950058.0720093</v>
+      <c r="BM18" t="n">
+        <v>327778579</v>
       </c>
     </row>
     <row r="19">
@@ -4062,16 +4118,16 @@
         <v>125000000</v>
       </c>
       <c r="C19" t="n">
-        <v>264808601.3078299</v>
+        <v>264808601.2631579</v>
       </c>
       <c r="D19" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>28966961.37738483</v>
+        <v>28966961.375</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -4083,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>198137254.9019608</v>
+        <v>56960784.31372549</v>
       </c>
       <c r="K19" t="n">
-        <v>1877348.40029762</v>
+        <v>1877348.375</v>
       </c>
       <c r="L19" t="n">
         <v>608333333.3333334</v>
@@ -4107,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4143,38 +4199,38 @@
         <v>0</v>
       </c>
       <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
         <v>153750000</v>
       </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
       <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
         <v>15000000</v>
       </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>44964000</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AK19" t="n">
         <v>18181818.18181818</v>
       </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
         <v>20000000</v>
       </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
@@ -4191,23 +4247,23 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
         <v>9583333.333333334</v>
       </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
       <c r="AV19" t="n">
         <v>0</v>
       </c>
       <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
         <v>14375000</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AY19" t="n">
         <v>13636363.63636364</v>
       </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
@@ -4224,20 +4280,20 @@
         <v>0</v>
       </c>
       <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
         <v>7000000</v>
       </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
       <c r="BG19" t="n">
         <v>0</v>
       </c>
       <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
         <v>120000000</v>
       </c>
-      <c r="BI19" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ19" t="n">
         <v>0</v>
       </c>
@@ -4245,7 +4301,10 @@
         <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>362950058.0720093</v>
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>327778579</v>
       </c>
     </row>
     <row r="20">
@@ -4256,16 +4315,16 @@
         <v>125000000</v>
       </c>
       <c r="C20" t="n">
-        <v>127966496.044672</v>
+        <v>127966496</v>
       </c>
       <c r="D20" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>28966961.37738483</v>
+        <v>28966961.375</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4277,10 +4336,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>143897058.8235294</v>
+        <v>49779411.76470588</v>
       </c>
       <c r="K20" t="n">
-        <v>1877348.40029762</v>
+        <v>1877348.375</v>
       </c>
       <c r="L20" t="n">
         <v>912500000</v>
@@ -4301,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>121322414.3160449</v>
+        <v>121322414.375</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4337,29 +4396,29 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
         <v>153750000</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
       <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
         <v>15000000</v>
       </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
       <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>120000000</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AK20" t="n">
         <v>6060606.060606061</v>
       </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
@@ -4376,11 +4435,11 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
         <v>1337500</v>
       </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
@@ -4403,11 +4462,11 @@
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
         <v>916666.6666666666</v>
       </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
       <c r="BB20" t="n">
         <v>0</v>
       </c>
@@ -4418,11 +4477,11 @@
         <v>0</v>
       </c>
       <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
         <v>7000000</v>
       </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
@@ -4439,7 +4498,10 @@
         <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>362950058.0720093</v>
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>327778579</v>
       </c>
     </row>
     <row r="21">
@@ -4450,16 +4512,16 @@
         <v>125000000</v>
       </c>
       <c r="C21" t="n">
-        <v>127966496.044672</v>
+        <v>127966496</v>
       </c>
       <c r="D21" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>28966961.37738483</v>
+        <v>28966961.375</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -4474,7 +4536,7 @@
         <v>26250000</v>
       </c>
       <c r="K21" t="n">
-        <v>1877348.40029762</v>
+        <v>1877348.375</v>
       </c>
       <c r="L21" t="n">
         <v>912500000</v>
@@ -4531,17 +4593,17 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
         <v>153750000</v>
       </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
         <v>15000000</v>
       </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
       <c r="AH21" t="n">
         <v>0</v>
       </c>
@@ -4570,11 +4632,11 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
         <v>1337500</v>
       </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
@@ -4597,11 +4659,11 @@
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
         <v>2750000</v>
       </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
       <c r="BB21" t="n">
         <v>0</v>
       </c>
@@ -4612,11 +4674,11 @@
         <v>0</v>
       </c>
       <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
         <v>7000000</v>
       </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
@@ -4633,7 +4695,10 @@
         <v>0</v>
       </c>
       <c r="BL21" t="n">
-        <v>362950058.0720093</v>
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>327778579</v>
       </c>
     </row>
   </sheetData>
